--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.436801249702837</v>
+        <v>2.436862621085749</v>
       </c>
       <c r="C2">
-        <v>1.700317937929736</v>
+        <v>1.693735203374959</v>
       </c>
       <c r="D2">
-        <v>1.457347192194636</v>
+        <v>1.453782206960007</v>
       </c>
       <c r="E2">
-        <v>1.346982622402223</v>
+        <v>1.346536947502336</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.442838613609139</v>
+        <v>2.442857341922114</v>
       </c>
       <c r="C3">
-        <v>1.703193982803088</v>
+        <v>1.696449200345058</v>
       </c>
       <c r="D3">
-        <v>1.458595287136383</v>
+        <v>1.455006096426903</v>
       </c>
       <c r="E3">
-        <v>1.34782820070677</v>
+        <v>1.347375920831563</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.416199608207933</v>
+        <v>2.416188954227599</v>
       </c>
       <c r="C4">
-        <v>1.689607354824598</v>
+        <v>1.682962049416409</v>
       </c>
       <c r="D4">
-        <v>1.451431135937861</v>
+        <v>1.4478970698214</v>
       </c>
       <c r="E4">
-        <v>1.342718102337792</v>
+        <v>1.342259846645607</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.44404084425824</v>
+        <v>2.444043537358676</v>
       </c>
       <c r="C5">
-        <v>1.705018684914926</v>
+        <v>1.698139667833802</v>
       </c>
       <c r="D5">
-        <v>1.446166112413757</v>
+        <v>1.442526263593065</v>
       </c>
       <c r="E5">
-        <v>1.349992015156981</v>
+        <v>1.349487807750695</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.451383197835506</v>
+        <v>2.451386007418045</v>
       </c>
       <c r="C6">
-        <v>1.709059898859096</v>
+        <v>1.702134782103341</v>
       </c>
       <c r="D6">
-        <v>1.448580771627434</v>
+        <v>1.444906103465592</v>
       </c>
       <c r="E6">
-        <v>1.351843737668599</v>
+        <v>1.351337705383488</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.443418879671671</v>
+        <v>2.443423707789303</v>
       </c>
       <c r="C7">
-        <v>1.705004603960501</v>
+        <v>1.698146787641202</v>
       </c>
       <c r="D7">
-        <v>1.46083899459511</v>
+        <v>1.45717066678732</v>
       </c>
       <c r="E7">
-        <v>1.349955890124775</v>
+        <v>1.349480192554219</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.4261378456398</v>
+        <v>2.426242503446296</v>
       </c>
       <c r="C8">
-        <v>1.691113062267858</v>
+        <v>1.685144340797455</v>
       </c>
       <c r="D8">
-        <v>1.463289021859106</v>
+        <v>1.460945855504326</v>
       </c>
       <c r="E8">
-        <v>1.340676964773854</v>
+        <v>1.340521949481359</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.437293282939875</v>
+        <v>2.437302669239246</v>
       </c>
       <c r="C9">
-        <v>1.699213878649834</v>
+        <v>1.692402558551635</v>
       </c>
       <c r="D9">
-        <v>1.455487230471161</v>
+        <v>1.451868550037982</v>
       </c>
       <c r="E9">
-        <v>1.34534416732288</v>
+        <v>1.344885643389748</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.354271173204168</v>
+        <v>2.354255988934814</v>
       </c>
       <c r="C10">
-        <v>1.667191889118646</v>
+        <v>1.661081076980147</v>
       </c>
       <c r="D10">
-        <v>1.444906915254569</v>
+        <v>1.441425113818204</v>
       </c>
       <c r="E10">
-        <v>1.339021721330762</v>
+        <v>1.338586669553266</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.358096505327884</v>
+        <v>2.360448614252602</v>
       </c>
       <c r="C11">
-        <v>1.671843872822301</v>
+        <v>1.665767752176606</v>
       </c>
       <c r="D11">
-        <v>1.447518338027816</v>
+        <v>1.444014140732595</v>
       </c>
       <c r="E11">
-        <v>1.340293742975245</v>
+        <v>1.339860055703738</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.233541039399723</v>
+        <v>2.233657609199229</v>
       </c>
       <c r="C12">
-        <v>1.617368168486356</v>
+        <v>1.611816605513263</v>
       </c>
       <c r="D12">
-        <v>1.424266206036189</v>
+        <v>1.420851866011045</v>
       </c>
       <c r="E12">
-        <v>1.324371252076056</v>
+        <v>1.32393441237671</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.342009859240122</v>
+        <v>2.34199469004214</v>
       </c>
       <c r="C13">
-        <v>1.659963471116275</v>
+        <v>1.65373929412394</v>
       </c>
       <c r="D13">
-        <v>1.440926698548765</v>
+        <v>1.437449491461344</v>
       </c>
       <c r="E13">
-        <v>1.336020726629191</v>
+        <v>1.335577775097917</v>
       </c>
     </row>
   </sheetData>
